--- a/FIG4_sidechain_and_grantham.xlsx
+++ b/FIG4_sidechain_and_grantham.xlsx
@@ -1394,127 +1394,131 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>167.7</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>6.700000000000017</v>
+      </c>
+      <c r="C3" t="n">
+        <v>97</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>167.7</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>54.40000000000001</v>
+      </c>
+      <c r="C4" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>119.3</v>
+        <v>52.59999999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>215</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>119.3</v>
+        <v>6.700000000000017</v>
       </c>
       <c r="C6" t="n">
-        <v>215</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>VD</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78.30000000000001</v>
+        <v>28.90000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>98</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GE</t>
+          <t>YD</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>78.30000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="C8" t="n">
-        <v>98</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.700000000000017</v>
+        <v>53.99999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IR</t>
+          <t>WG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.700000000000017</v>
+        <v>167.7</v>
       </c>
       <c r="C10" t="n">
-        <v>97</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>WL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>54.40000000000001</v>
+        <v>61.10000000000002</v>
       </c>
       <c r="C11" t="n">
-        <v>101</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>WR</t>
+          <t>AD</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54.40000000000001</v>
+        <v>22.5</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13">
@@ -1557,118 +1561,118 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>IV</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4000000000000057</v>
+        <v>26.69999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26.69999999999999</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>26.69999999999999</v>
+        <v>0.4000000000000057</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>3.399999999999991</v>
       </c>
       <c r="C19" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>27.09999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>PS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4000000000000057</v>
+        <v>23.7</v>
       </c>
       <c r="C21" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>QE</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4000000000000057</v>
+        <v>5.400000000000006</v>
       </c>
       <c r="C22" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>QR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26.69999999999999</v>
+        <v>29.59999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IV</t>
+          <t>KN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>26.69999999999999</v>
+        <v>54.5</v>
       </c>
       <c r="C24" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
@@ -1698,128 +1702,130 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>RQ</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>29.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>43</v>
+        <v>205</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29.59999999999999</v>
-      </c>
-      <c r="C28" t="n">
-        <v>43</v>
-      </c>
+        <v>48.4</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>HN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>138.8</v>
+        <v>39.09999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>177</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SW</t>
+          <t>KM</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>138.8</v>
+        <v>5.699999999999989</v>
       </c>
       <c r="C30" t="n">
-        <v>177</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>46.80000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>81</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>46.80000000000001</v>
+        <v>40.49999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>QE</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>81.40000000000001</v>
+        <v>5.400000000000006</v>
       </c>
       <c r="C33" t="n">
-        <v>205</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>QK</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>81.40000000000001</v>
+        <v>24.79999999999998</v>
       </c>
       <c r="C34" t="n">
-        <v>205</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>VE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="C35" t="inlineStr"/>
+        <v>1.599999999999994</v>
+      </c>
+      <c r="C35" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="C36" t="inlineStr"/>
+        <v>3.399999999999991</v>
+      </c>
+      <c r="C36" t="n">
+        <v>38</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1861,118 +1867,118 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>RP</t>
+          <t>WC</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>60.7</v>
+        <v>119.3</v>
       </c>
       <c r="C40" t="n">
-        <v>103</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>119.3</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>215</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>WC</t>
+          <t>WR</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>119.3</v>
+        <v>54.40000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>215</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>GE</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>167.7</v>
+        <v>78.30000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>181</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>WG</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>167.7</v>
+        <v>52.59999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>181</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>IR</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>64.90000000000001</v>
+        <v>6.700000000000017</v>
       </c>
       <c r="C45" t="n">
-        <v>180</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RC</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>64.90000000000001</v>
+        <v>77.69999999999999</v>
       </c>
       <c r="C46" t="n">
-        <v>180</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WL</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>61.10000000000002</v>
+        <v>53.99999999999999</v>
       </c>
       <c r="C47" t="n">
-        <v>61</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>WL</t>
+          <t>LR</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>61.10000000000002</v>
+        <v>6.700000000000017</v>
       </c>
       <c r="C48" t="n">
-        <v>61</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49">
@@ -2013,112 +2019,118 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>167.7</v>
-      </c>
-      <c r="C52" t="inlineStr"/>
+        <v>54.40000000000001</v>
+      </c>
+      <c r="C52" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>VM</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>167.7</v>
-      </c>
-      <c r="C53" t="inlineStr"/>
+        <v>22.90000000000001</v>
+      </c>
+      <c r="C53" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GW</t>
+          <t>TS</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>167.7</v>
-      </c>
-      <c r="C54" t="inlineStr"/>
+        <v>27.09999999999999</v>
+      </c>
+      <c r="C54" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>TK</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>54.40000000000001</v>
+        <v>52.5</v>
       </c>
       <c r="C55" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>KN</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>54.40000000000001</v>
+        <v>54.5</v>
       </c>
       <c r="C56" t="n">
-        <v>101</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>54.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="C57" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>QP</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>54.40000000000001</v>
+        <v>31.10000000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>CG</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>22.90000000000001</v>
+        <v>48.4</v>
       </c>
       <c r="C59" t="n">
-        <v>21</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>VM</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>22.90000000000001</v>
+        <v>61.10000000000002</v>
       </c>
       <c r="C60" t="n">
-        <v>21</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61">
@@ -2161,111 +2173,111 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>26.69999999999999</v>
+        <v>27.09999999999999</v>
       </c>
       <c r="C64" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>ED</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.69999999999999</v>
+        <v>27.30000000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>26.69999999999999</v>
+        <v>49.80000000000001</v>
       </c>
       <c r="C66" t="n">
-        <v>32</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EQ</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>27.09999999999999</v>
+        <v>5.400000000000006</v>
       </c>
       <c r="C67" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>27.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="C68" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>27.09999999999999</v>
+        <v>0.4000000000000057</v>
       </c>
       <c r="C69" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>27.09999999999999</v>
+        <v>27.5</v>
       </c>
       <c r="C70" t="n">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>27.30000000000001</v>
+        <v>3.399999999999991</v>
       </c>
       <c r="C71" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ED</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -2538,7 +2550,7 @@
         <v>0.01017</v>
       </c>
       <c r="G13" t="n">
-        <v>0.00194</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="14">
@@ -2549,14 +2561,18 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="n">
-        <v>0.02837</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.04937</v>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>0.0015</v>
+        <v>0.00283</v>
       </c>
       <c r="G14" t="n">
         <v>0.00016</v>
@@ -2580,7 +2596,7 @@
         <v>0.01726</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0032</v>
+        <v>0.00911</v>
       </c>
     </row>
     <row r="16">
@@ -2594,10 +2610,10 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
-        <v>0.0025</v>
+        <v>0.0058</v>
       </c>
       <c r="G16" t="n">
-        <v>0.00016</v>
+        <v>0.0015</v>
       </c>
     </row>
     <row r="17">
@@ -2731,16 +2747,20 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
-        <v>0.04937</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>ns</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>0.04937</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -2757,8 +2777,10 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.04937</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -2868,8 +2890,10 @@
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="n">
-        <v>0.01556</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2887,7 +2911,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0.00016</v>
+        <v>0.02334</v>
       </c>
     </row>
     <row r="14">
@@ -2903,14 +2927,18 @@
           <t>ns</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.01017</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
       </c>
       <c r="G14" t="n">
-        <v>0.00016</v>
+        <v>0.0065</v>
       </c>
     </row>
     <row r="15">
@@ -2933,7 +2961,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0.00016</v>
+        <v>0.00516</v>
       </c>
     </row>
     <row r="16">
@@ -2952,7 +2980,7 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0.00016</v>
+        <v>0.00407</v>
       </c>
     </row>
     <row r="17">
@@ -2966,8 +2994,10 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
-      <c r="G17" t="n">
-        <v>0.02837</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ns</t>
+        </is>
       </c>
     </row>
     <row r="18">
